--- a/samples/構築結果報告書_template_sample.xlsx
+++ b/samples/構築結果報告書_template_sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="構築結果" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リスト" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="構築結果" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="リスト" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -90,6 +90,9 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -458,14 +461,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E22"/>
+  <dimension ref="B1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -533,6 +537,11 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
           <t>備考</t>
         </is>
       </c>
@@ -545,7 +554,8 @@
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
@@ -555,7 +565,8 @@
       </c>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
@@ -565,7 +576,8 @@
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="3" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
@@ -573,9 +585,10 @@
           <t>vCPU</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n"/>
+      <c r="C12" s="8" t="n"/>
       <c r="D12" s="3" t="n"/>
-      <c r="E12" s="3" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
@@ -583,9 +596,10 @@
           <t>メモリ(GiB)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n"/>
+      <c r="C13" s="8" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
@@ -595,7 +609,8 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
@@ -605,7 +620,8 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="3" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
@@ -615,7 +631,8 @@
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
@@ -625,7 +642,8 @@
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
@@ -635,7 +653,8 @@
       </c>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
@@ -643,9 +662,10 @@
           <t>EBSサイズ(GiB)</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n"/>
+      <c r="C19" s="8" t="n"/>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -669,11 +689,11 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:E1"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
     <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">

--- a/samples/構築結果報告書_template_sample.xlsx
+++ b/samples/構築結果報告書_template_sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="構築結果" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="リスト" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="構築結果" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リスト" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -90,9 +90,6 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -461,15 +458,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F22"/>
+  <dimension ref="B1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -537,11 +533,6 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
           <t>備考</t>
         </is>
       </c>
@@ -554,8 +545,7 @@
       </c>
       <c r="C9" s="3" t="n"/>
       <c r="D9" s="3" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
@@ -565,8 +555,7 @@
       </c>
       <c r="C10" s="3" t="n"/>
       <c r="D10" s="3" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="3" t="n"/>
+      <c r="E10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
@@ -576,8 +565,7 @@
       </c>
       <c r="C11" s="3" t="n"/>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
@@ -585,10 +573,9 @@
           <t>vCPU</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n"/>
+      <c r="C12" s="7" t="n"/>
       <c r="D12" s="3" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="3" t="n"/>
+      <c r="E12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
@@ -596,10 +583,9 @@
           <t>メモリ(GiB)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n"/>
+      <c r="C13" s="7" t="n"/>
       <c r="D13" s="3" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
@@ -609,8 +595,7 @@
       </c>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="3" t="n"/>
+      <c r="E14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
@@ -620,8 +605,7 @@
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
@@ -631,8 +615,7 @@
       </c>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="3" t="n"/>
+      <c r="E16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
@@ -642,8 +625,7 @@
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="3" t="n"/>
+      <c r="E17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
@@ -653,8 +635,7 @@
       </c>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="3" t="n"/>
+      <c r="E18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
@@ -662,10 +643,9 @@
           <t>EBSサイズ(GiB)</t>
         </is>
       </c>
-      <c r="C19" s="8" t="n"/>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="3" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
@@ -689,11 +669,11 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="B1:E1"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="B1:F1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D9 D10 D11 D12 D13 D14 D15 D16 D17 D18 D19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"OK,NG,対象外"</formula1>
     </dataValidation>
     <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
